--- a/AAII_Financials/Quarterly/VALE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VALE_QTR_FIN.xlsx
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10232400</v>
+      </c>
+      <c r="E8" s="3">
         <v>9331500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10834400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10639300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9140900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8269100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9604200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9729300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9318900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8352300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13293700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10404700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9904800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8658200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11275400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9622300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10157000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11663100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14152100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12973800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>30164500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12870300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14972500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>11278900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7967900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5578900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7576200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7627900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6375400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5792000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6682000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7005700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7293600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6522800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7647100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7332500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5989800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6634200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7604100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5416000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7109500</v>
+      </c>
+      <c r="E9" s="3">
         <v>6215200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6640900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6769400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6317200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5548300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5944000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6395900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5968400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5302400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7024500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6177500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6088300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5080300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6758000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6105000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5427700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4970900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6208900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5766400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10135500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4412900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4535000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5043500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4466800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3430200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4280600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4244500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3591400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3321500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3914200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4223700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4544900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3962900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4828000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4383800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4220500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3560000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4062900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3727900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3122900</v>
+      </c>
+      <c r="E10" s="3">
         <v>3116300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4193500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3869900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2823700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2720900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3660200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3333400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3350600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3049900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6269200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4227200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3816500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3578000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4517300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3517300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4729300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6692200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7943100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>7207400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>20029000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8457400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10437500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6235400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3501100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2148700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3295500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3383400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2784100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2470400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2767800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2781900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2748700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2559900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2819100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2948600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1769200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3074200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3541300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1688100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,52 +1249,53 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E12" s="3">
         <v>131300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>-442400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>153900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>164800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>125400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>-456900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>195800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>178000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>153900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>741500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>183600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>169200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>142800</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
@@ -1358,8 +1372,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,252 +1497,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E14" s="3">
         <v>231900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3728200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>584900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>211400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>418400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1694900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-945600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-936500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>155500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>497100</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>395700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>149500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>524500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>366700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>318900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-924500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-283800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>238300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>474400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>241500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5472700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>432900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>582000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>150600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4454700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>191800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1048500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3240200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>196900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>130900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>402500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>136300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>186000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>127800</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>2084300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>133900</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>846000</v>
+      </c>
+      <c r="E15" s="3">
         <v>790700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>802800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>733700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>755200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>670100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>694400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>706900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>693100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>643400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>808500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>706800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>741600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>615400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>10700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>13100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>19600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>9000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>9400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>9700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>14000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>14600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>10700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>9200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>10300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>10500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>12400</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>13300</v>
       </c>
       <c r="AJ15" s="3">
         <v>13300</v>
       </c>
       <c r="AK15" s="3">
+        <v>13300</v>
+      </c>
+      <c r="AL15" s="3">
         <v>18200</v>
       </c>
-      <c r="AL15" s="3">
-        <v>0</v>
-      </c>
       <c r="AM15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="3">
         <v>18500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>22300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>102600</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7985800</v>
+      </c>
+      <c r="E17" s="3">
         <v>6707100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7839900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7201000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6846600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6011700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7238000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6981200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6583900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5783100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7555800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7193700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6569700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5554100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7910800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6806200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6305700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4359400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7807600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6331800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11974900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5023200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11155700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6076200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6328100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4146900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9518900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4836000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5618400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6989800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4666600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4597100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5190500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4285100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5681300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4816100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4773800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3636500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5701000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3729700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2246600</v>
+      </c>
+      <c r="E18" s="3">
         <v>2624400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2994600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3438300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2294300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2257400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2366200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2748100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2735100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2569200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5737900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3211000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3335100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3104200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3364500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2816100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3851300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7303800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6344500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6642000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18189600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7847100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3816900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5202600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1639800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1432000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1942700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2791900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>757000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-1197800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2015400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2408500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2103100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2237700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1965800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2516400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1215900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2997700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1903100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1686400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,618 +2086,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>142300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-328900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-383300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-334800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-465900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>723900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>891100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>302300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1622500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>73500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-69700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>373700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-468600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2390100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>890000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-108000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3792300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-201400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>728600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-17200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-585200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1215100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-301200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1712500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-491600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-678000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-321500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-333600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>148100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-755700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2342400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-210700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-855000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>440700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-741700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-143800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-221800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-604200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2950300</v>
+      </c>
+      <c r="E21" s="3">
         <v>3744100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4180600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4174800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3384200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3393400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3066300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2731000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2537100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2910400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4923900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3844300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4146500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3345900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3746800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5958000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5478900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7934200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10991200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7177100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>20562000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>8580400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4097300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4798000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2193200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>375800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1650100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2805900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1106000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-964600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2684000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2277600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>487300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2688700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1923000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3704700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1219400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3561300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2509400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1769700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E22" s="3">
         <v>363800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1870200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>309800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>316200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>300200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1698500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>277300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>266000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>251400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>472600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>290900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>294700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>321900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>149700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>142100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>146000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>175000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>145900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>164300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>365800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>138000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>222400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>209100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>159600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>148300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>176500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>180600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>150800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>165600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>161700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>209900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>209200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>213800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>247700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>370900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>270200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>286300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>236900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1716700</v>
+      </c>
+      <c r="E23" s="3">
         <v>2468800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2104000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2669500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2199900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2104800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-940000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2780800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2584700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2102900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3211100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2919800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2798600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2349600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2746300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5064100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4595400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7020800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9990900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6276200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18552500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7812500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3093700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3765100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1129500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-440100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2582700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1937400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>254900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1682200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1997900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1491200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-449200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1817800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>897000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2709500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>103300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2583700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1395100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>845300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>357700</v>
+      </c>
+      <c r="E24" s="3">
         <v>513700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2111700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-83300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-36700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>679300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-9100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>343600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-42700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>441600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>717000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>123300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1813100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>427200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-787400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>772500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>812800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2259100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1265000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>487600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4060000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1861500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>512100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>829300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>168500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-553800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1069500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>725400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>329100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-457400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-617700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>453600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-535800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>546300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-132000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>784800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-39800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>549700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>38400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>350900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1359100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1955100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4215700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2752800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2236600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1425500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-931000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2437200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2627400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1661300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2494100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2796500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>985500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1922400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3533700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4291600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3782600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4761800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8725900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5788600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>14492400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5951000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2581600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2935800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>961100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>113700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1513200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1212000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-74200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1224900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2615600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1037600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>86500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1271500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1029000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1924700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>143100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2034000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1356700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>494400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1321600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1907900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3821400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2742700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2217200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1423900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-756200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2458300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2628400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1653100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2469300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2776100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>948400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1880300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3515300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4302300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3736000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4737700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8648800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5757400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14466500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5937300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2681100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3041500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1042100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>175700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1183400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1227100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1201700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2584300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1064500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>80600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1257000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1066000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1917800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>115000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2021400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1383900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>488600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3202,28 +3263,28 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>1812900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-2519800</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1688500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-784800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-219100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1736800</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3231,8 +3292,8 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3244,37 +3305,40 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-100</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-9100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-63300</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-416600</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-86500</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-99500</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-63800</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-993600</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-31600</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,252 +3584,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E32" s="3">
         <v>328900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>383300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>334800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>465900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-723900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-891100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-302300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1622500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-73500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>69700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-373700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>468600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2390100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-890000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>108000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3792300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>201400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-728600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>17200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>585200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1215100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>301200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1712500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>491600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>678000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>321500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>333600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-148100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>755700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2342400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>210700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>855000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-440700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>741700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>143800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>221800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>604200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1321600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1907900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3821400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2742700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2217200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1423900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-756200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2458300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2628400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1653100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2469300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2776100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>948400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1880300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3515300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4302300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5548900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4738900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6129000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4068900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>13681700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5718200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>944300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3041500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1042100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>175700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1183400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1227100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1201700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2584200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1064500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>71500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1193800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>649400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1831300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>15500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1957600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>390300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>457000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1321600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1907900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3821400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2742700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2217200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1423900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-756200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2458300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2628400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1653100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2469300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2776100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>948400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1880300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3515300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4302300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5548900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4738900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6129000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4068900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>13681700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5718200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>944300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3041500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1042100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>175700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1183400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1227100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1201700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2584200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1064500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>71500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1193800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>649400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1831300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>15500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1957600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>390300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>457000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,213 +4306,217 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5572700</v>
+      </c>
+      <c r="E41" s="3">
         <v>5087500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7364400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5890200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5522900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3960900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4959000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4598400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6487900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3775300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3601200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3977500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4980200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4720300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4441300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5176100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6953100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8827900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13202200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11894100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13220000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13732100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13715700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9717500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13071600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10940500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5472100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6686200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4103800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3651500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3998400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4519200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5734600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4166300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3670700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3832600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4851300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5278900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3446000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2352300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>187400</v>
+      </c>
+      <c r="E42" s="3">
         <v>194000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>193500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>188000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>182400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>43400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>53500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>53300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>60900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>51500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>60900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>46700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>53500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>57500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>41600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>46700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>41900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>207500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>570700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>921500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1523100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>783900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>137800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>99900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>444100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>614800</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>8</v>
@@ -4440,8 +4530,8 @@
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ42" s="3">
         <v>0</v>
@@ -4455,871 +4545,895 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
-      <c r="AN42" s="3" t="s">
-        <v>8</v>
+      <c r="AN42" s="3">
+        <v>0</v>
       </c>
       <c r="AO42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AP42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ42" s="3">
         <v>1971200</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4328100</v>
+      </c>
+      <c r="E43" s="3">
         <v>3760400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3797900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3730400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3666100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3241800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3461800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3716700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2995500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3061100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5084600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4715600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4466300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4046200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5243800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3004800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2798200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3853500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5378800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1859100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5445700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4401500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5847600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4169800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3709800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2728400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2807800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2956900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3056800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3287800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3067600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3244000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3929800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3695900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5471000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5103900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4454100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>5326500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>4461500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3658600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6258500</v>
+      </c>
+      <c r="E44" s="3">
         <v>6138000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5930600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5555400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5250000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4926500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4610100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4948200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4799700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5175200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4673900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5127900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5190300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5008800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4203200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5262000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4988000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4908600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4930700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5570500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4552800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4556100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4129800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4756100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4378900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3795800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3182100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3616000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3205900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3579800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3071300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3004600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3600300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3078800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3329700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3316000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3277300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2862100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2707400</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>3140400</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1297500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1579200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>986000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1088500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2990600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2537700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>412300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>490700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>505400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5404400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5245800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>830400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>855300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>728000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>614000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>422500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>719800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1331000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1470400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2005000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>464200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>487600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>338800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>493800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>651900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>600500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>611600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1181900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>432900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>473400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>433900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>442300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>662200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>886800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3603900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3900800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4262900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4157200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>7630700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>4587000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17644200</v>
+      </c>
+      <c r="E46" s="3">
         <v>16759000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18272500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16452500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17612000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14710400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13496700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13807200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14849400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17460100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18656900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14712200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15538700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14556700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14559700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13906900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15505800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18963000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>25189600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>21899500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>24604200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>24700400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>24815800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>19274900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>21912100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18509400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12688400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14441000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>10799300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>10992400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>10571300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>11210200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13927000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>11827800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>16075200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>16153400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>16845500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>17624700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>18245600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>15709500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5259400</v>
+      </c>
+      <c r="E47" s="3">
         <v>5222200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5024300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5205100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4791500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4632400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4552700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4099400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3766500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1930400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1912100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1958700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1930400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1781000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1686000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1793300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1732700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1877400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1972200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3809000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3579700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3027300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3064700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5915300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5670400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3566600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3338800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3661200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3267100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3663100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3448900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3634400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4463000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4230800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5382600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5425000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>5465700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5299900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>3135400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>3364300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46361200</v>
+      </c>
+      <c r="E48" s="3">
         <v>45689800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>43580200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45204300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>44361000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41997000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40032000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46094200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44640500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>47370000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>48286800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>47878900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>48641100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46184700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42141700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>42150200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41775500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>45115200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>47229600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>45011200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>42505300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>41636300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>41847700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41737500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41234400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>36354000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>34674300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>38174800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>34360800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>36388200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>33446700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>35140300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>43858900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>42028700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>46541900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>45711500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>46359000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>44231600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>44807200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>49226600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9413400</v>
+      </c>
+      <c r="E49" s="3">
         <v>9366600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8943500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10913000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10736900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10197300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10526400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11546900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10208400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11214800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11604600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10611500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10995500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10482500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9601400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9334100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9143200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10002000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10149900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9764500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10651500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9231500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9454000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7266700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7236900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6400400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6327300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6490100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5864100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6227400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5503700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5771100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7193600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>6669200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7202800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7026100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>6116100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5742700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5555600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5603900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4515900</v>
+      </c>
+      <c r="E52" s="3">
         <v>4333400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4305200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4274800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4030200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3697400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3386000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3504700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3320100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3686200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3969000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4359500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4463800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3999000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13498400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13340000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13482100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14790100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16202700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14692400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12335400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14120500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14387800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13678600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>13668200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>13666100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11249300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10580700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10670200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11382200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7991400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7575700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9872000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8500200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8915000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8603700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>8591300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>8068500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>8310700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>8308600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>89206500</v>
+      </c>
+      <c r="E54" s="3">
         <v>87636000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>86436800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>90995800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>90520100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>83556600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>80247900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>88933000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>86728700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>91323500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>93972800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>89229500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>91469000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>87839000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>81487200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>80524500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>81639300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>90747800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100744000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>95176500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>93676100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>92716000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>93569900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>87873000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>89722100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>78496500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>68278100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>73347700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>64961600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>68653400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>60961900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>63331800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>79314400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>73256700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>84117400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>82919700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>83377600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>80967300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>80054500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>82213000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,740 +6146,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6198500</v>
+      </c>
+      <c r="E57" s="3">
         <v>5493300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5559400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5639300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5462100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4409500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4238900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5355900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4775700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5524900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5260000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5597600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5237200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4479100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4558700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4865500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3711500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3727500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4356700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4632800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3840500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4093700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4159700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4225600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3969100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3586900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3787600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3911300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3192200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3232300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3211600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3364900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3721200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3451600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3656100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3671200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3613400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3632600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3477900</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3470000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1261200</v>
+      </c>
+      <c r="E58" s="3">
         <v>757900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>677400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>643400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>860700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>784200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1167800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>999000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1089100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1472800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1018100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>978800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>911500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>545100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>458700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>445600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>905100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1075000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1356400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1473800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>960900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1053900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1154900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1124800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1303300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1081900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1072100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1224700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1035000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2139900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>693700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1017200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1641000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1525900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1444300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1493200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1749300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1891800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1342000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1756400</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6459600</v>
+      </c>
+      <c r="E59" s="3">
         <v>6275000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8484700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5739300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7378300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7396500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6685500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7713200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6959800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7104400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6499000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5952000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6394200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7383600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8009100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7668800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7109700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9487200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11405800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11504200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9081500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7458300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9526800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6386900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>6762700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6075600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5447600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5355300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4480400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3717300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2430900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2411800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2909200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2776400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6015600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3540800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3612600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3770200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4262100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3507600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14805200</v>
+      </c>
+      <c r="E60" s="3">
         <v>13516500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15853300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13296100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14491600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13254700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13105300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15181300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13759800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15616600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14621500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13680500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13549000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13020200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13026500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12979900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11726300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14289600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17118900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17610900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13882900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12606000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14841400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11737400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12035100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10744500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10307300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10491300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8707600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9089500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6336200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6794000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>8271400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7754000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>11116000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>8705200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>8975400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>9294600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>9082100</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>8734100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19972400</v>
+      </c>
+      <c r="E61" s="3">
         <v>20703400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>20357500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>20525600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19469800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17788600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16575200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15600700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16515400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15755000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15740200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15506900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15544500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15338200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11462800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11744300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11296800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12579400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14166900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13408700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12466000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>13664000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14127100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15428000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>18719600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16336900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9980800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11740200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10927700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11567200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9997400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11436400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14481900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>14211900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>17628400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>19453700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>21873800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>21350800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>22365300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>23570000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12361000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12615600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12639800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9668800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12703700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12846300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12563000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14235500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11496700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14061200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15264900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13737000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14990600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16147300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21969700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21160400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22825300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>26379900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>29684000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>26803700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>26291800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>28672100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>29182500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24213200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>23422600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>20549700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18964500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17782200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>15935900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16510200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13643400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14258200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>17951400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>15742900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>17401700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>17013600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>16990600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>16074300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>15438300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>16222000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50319300</v>
+      </c>
+      <c r="E66" s="3">
         <v>50080800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52136500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48827300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>49967100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47153600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45692700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>49214400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48306300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52476700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53100400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>49649400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51210600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>48838900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>47857600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47353100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>47283000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>54081100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>61909400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>58663400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>53316500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>53897300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57211800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>49961000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>52879900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46567500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>38452700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>40540500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>36074500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>37759800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>30562100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33124200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>41550700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>38565900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>47260900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>46370100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>49052200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>47925500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>48488600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>50227100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20366000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19009100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17461700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24865300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23122700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19867400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18575700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22366100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21136600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20486500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21882600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20871000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20458600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18578500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19240600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17482900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19769000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15815800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17434500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10684200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15577300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10565000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7396700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7901300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7350400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5702100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5717700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8104800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6492300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6933100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>7755300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5363300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>7222100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>7146900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6553000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>7109800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4470600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4822700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2946700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3414000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>37954600</v>
+      </c>
+      <c r="E76" s="3">
         <v>36654400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33460200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>40929000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>39306800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35245800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>33431700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>38300700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37007500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37326500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>39355600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>38079300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>38780500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37459900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>33629600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>33171400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34356300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>36666700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>38834600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>36513100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>40359600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>38818700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36358100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>37911900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36842200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>31929000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29825400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>32807200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>28887100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>30893600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>30399800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>30207600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>37763700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>34690800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>36856600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>36549600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>34325300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>33041800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>31565800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>31985900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1321600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1907900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3821400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2742700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2217200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1423900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-756200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2458300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2628400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1653100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2469300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2776100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>948400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1880300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3515300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4302300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5548900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4738900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6129000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4068900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>13681700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5718200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>944300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3041500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1042100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>175700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1183400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1227100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1201700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2584200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1064500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>71500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1193800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>649400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1831300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>15500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1957600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>390300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>457000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>733700</v>
+      </c>
+      <c r="E83" s="3">
         <v>629100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>678600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>677300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>674000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>627500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>795700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>691200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>723600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>831300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>751800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>763100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>679800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>850800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>751800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>737600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>738400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>854400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>736500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1643800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>750500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>881700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>810500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>854500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>656300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>784300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>692000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>670400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>566900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>520500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>624700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>726600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>661700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>812200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>747600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>745200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>707400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>598500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>775800</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2383600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1874200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2677000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2575900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1939100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1696300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2765800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1679600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1103300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3553400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4865500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2820500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1915500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3747200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1795000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3109100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3253800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2832600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2116000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9526000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15293600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7167300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6815300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4990000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1385300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1380700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2067400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3051200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2047500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1546000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2227400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2857700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3016300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1654300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3075400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1940400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2841900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2379500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2108400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1213700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1196900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2148000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1404500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1232200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1283700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2180500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1423300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1253000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1376900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2083300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1500000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1239000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1159700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9392000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6455000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6373000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5964000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6067900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6526200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-606800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-586300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1336100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-914000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-892400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1066900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-717900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-507300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-431500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1024000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-520500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-592700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-674300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-816500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-695500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-731200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-865000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>2329500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1929200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1778700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1281800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2227100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1273300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2087400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1401600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3601700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1356200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1152500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1499000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2265900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1656400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1091700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1361500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1748200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-982000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1031100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-730600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-433300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-848200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5601600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2454800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2050500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1054400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-713100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-843300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-968200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-406600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-414400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3141400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1049900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-508600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-366500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>2166300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-687700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-404900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-949700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-675900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1063200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-533700</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,130 +10456,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>2772800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>93500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1518200</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>1982200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1641800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>2337200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2067700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1657400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>1866100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-3004000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-6500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3670300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-25900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-8099500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-6378700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-4090900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-31500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3604700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-5800</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-2100</v>
       </c>
       <c r="AC96" s="3">
         <v>-2100</v>
       </c>
       <c r="AD96" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-74100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-44400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1481900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1170100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-1192300</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-2200</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-436800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>49700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-109100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3045000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>943400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-987700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1647900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1338100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1344900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2344500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>403700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1846500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2268800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2102100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-632800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2457600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-538500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3994000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3560700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5576700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-620300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11266200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9722800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5138400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-214600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7505800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-181400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4018700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2099200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-718600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-939400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1051500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1389000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2527100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1534500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2563500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2373000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2436100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>179900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1931600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-446800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-253100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-242100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>469200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-72000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>417700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>83300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-122400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>107100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-167800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-88100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-107400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>89800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>371600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1174100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-102100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>89800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>359200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1147400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>219500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>732000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-319700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1045800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-597600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>367200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>504300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1095300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-111400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>412800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-45000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-147400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>153200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>453300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-75200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>89000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-96000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>57700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-50600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>8800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>47800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>449900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2688100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1545800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>367000</v>
       </c>
-      <c r="G102" s="3">
-        <v>1355000</v>
-      </c>
       <c r="H102" s="3">
+        <v>1246500</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1285400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>978200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2093000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3077100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>291300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>208400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-830800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-160000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-593800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1777000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-978900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4622200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1282000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1856400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-350600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>619800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3952500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3202900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>994900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5651400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1111400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2338800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>648600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-542600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-358900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-24600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1568300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>822900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-161900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1018600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-604200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1832900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-877500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1005000</v>
       </c>
     </row>
